--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260709.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260709.xlsx
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>200,000</t>
+          <t>8,500,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>8,500,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
